--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -8,47 +8,799 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\scripts\Amazon_Price_search\Amazon_Price_search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{914BDA38-EE0B-4010-B035-196FEEF292E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B685F0E-C2E9-4BAB-8173-D94C2A9D7582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{F15C011C-DCB2-48C8-8CB7-81B104D1E5D7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E8086195-D835-47BE-A19B-ADA8C2D35C96}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="items - 2026-02-20T162513.898" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>JAN</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="208">
+  <si>
+    <t>商品コード</t>
+  </si>
+  <si>
+    <t>商品名</t>
+  </si>
+  <si>
+    <t>入数</t>
+  </si>
+  <si>
+    <t>上代(税抜)</t>
+  </si>
+  <si>
+    <t>卸値</t>
+  </si>
+  <si>
+    <t>JANコード</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　シナモロール</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃんフィギュばし！　しんちゃん</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃんフィギュばし！　パジャマ</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃんフィギュばし！　チョコビ</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃんフィギュばし！　シロ</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　ポチャッコ</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　ポムポムプリン</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　ハンギョドン</t>
+  </si>
+  <si>
+    <t>サンリオフィギュばし！　ぐでたま</t>
+  </si>
+  <si>
+    <t>ミッフィーポケット付きエコバッグ　ピンク</t>
+  </si>
+  <si>
+    <t>ミッフィーポケット付きエコバッグ　グレー</t>
+  </si>
+  <si>
+    <t>サンリオタータンチェックハート型ポシェット　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオタータンチェックハート型ポシェット　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみペンポーチ　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオフェイスポーチ　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみペンポーチ　ウサハナ</t>
+  </si>
+  <si>
+    <t>サンリオフェイスポーチ　ウサハナ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみペンポーチ　しろうさ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみペンポーチ　くろうさ</t>
+  </si>
+  <si>
+    <t>サンリオフェイスポーチ　しろうさ</t>
+  </si>
+  <si>
+    <t>サンリオフェイスポーチ　くろうさ</t>
+  </si>
+  <si>
+    <t>サンリオフェイスミニがま口　チョコキャット</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　フェイス</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　ジョークール</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　フレンズフェイス</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　ちらし</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　レシピ</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　スヌーピーいっぱい</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　ラッパ</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　バケツ</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　タイプライター</t>
+  </si>
+  <si>
+    <t>スヌーピー巾着　スリーフェイス</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみ巾着　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオフェイスミニがま口　ウサハナ</t>
+  </si>
+  <si>
+    <t>ミッフィーソックス　ちらしライトグレー</t>
+  </si>
+  <si>
+    <t>ミッフィーソックス　ちらしダークグレー</t>
+  </si>
+  <si>
+    <t>ミッフィーソックス　ちらしベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　オラフペールグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　スパイクカーキ</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　アンディグレーベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　マーブルスピンクグレージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーホワイト</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーアイボリー</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーダークグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　ジョークールダークブルー</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　スヌーピーブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーくすみベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　ウッドストックくすみピンク</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　ジョークールくすみブルー</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　チャーリーくすみグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　ウッドストックグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　オラフグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーラバープリントソックス　アローホワイト</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　スヌーピーくすみブルー</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　スヌーピーホワイト</t>
+  </si>
+  <si>
+    <t>スヌーピータグ付きソックス　ジョー・クールブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーラバープリントソックス　スヌーピーピンクグレージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーラバープリントソックス　チャーリー・ブラウングレー</t>
+  </si>
+  <si>
+    <t>スヌーピーもふもふソックス　ウッドストック</t>
+  </si>
+  <si>
+    <t>スヌーピーラバープリントソックス　オラフスモークブルー</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　チャーリーブラウン</t>
+  </si>
+  <si>
+    <t>スヌーピーバックポイントソックス　スヌーピーライトグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　スヌーピーベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーちらし柄ソックス　ウッドストックブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーラインアートソックス　スヌーピーアイボリー</t>
+  </si>
+  <si>
+    <t>スヌーピータグ付きソックス　くすみベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピータグ付きソックス　ピンクグレージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーくるくるソックス　スヌーピーグレー</t>
+  </si>
+  <si>
+    <t>スヌーピーくるくるソックス　スヌーピーブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーライン刺繍ソックス　ブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーレイヤーソックス　ホワイト</t>
+  </si>
+  <si>
+    <t>スヌーピーレイヤーソックス　ブラック</t>
+  </si>
+  <si>
+    <t>スヌーピーレイヤーソックス　ベージュ</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　オラフ</t>
+  </si>
+  <si>
+    <t>スヌーピーフットプリントソックス　ウッドストック</t>
+  </si>
+  <si>
+    <t>スヌーピーフロートソックス　アイボリー</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　ジンベエザメ</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　ヤンバルクイナ</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　チンアナゴ</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　黒シーサー</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　白シーサー</t>
+  </si>
+  <si>
+    <t>沖縄バックポイントソックス　ハイビスカス</t>
+  </si>
+  <si>
+    <t>スヌーピー３ポイントデザインソックス　ブラザーズ</t>
+  </si>
+  <si>
+    <t>スヌーピー３ポイントデザインソックス　ウッドストック</t>
+  </si>
+  <si>
+    <t>スヌーピーラン型エプロン　ブラザーズ</t>
+  </si>
+  <si>
+    <t>ミッフィーラン型エプロン　おうち</t>
+  </si>
+  <si>
+    <t>ミッフィーラン型エプロン　ミッフィーと月</t>
+  </si>
+  <si>
+    <t>ミッフィーラン型エプロン　おえかき</t>
+  </si>
+  <si>
+    <t>スヌーピーラン型エプロン　コミック</t>
+  </si>
+  <si>
+    <t>スヌーピーラン型エプロン　クッキー</t>
+  </si>
+  <si>
+    <t>スヌーピーＸ型エプロン　スヌーピーネイビー</t>
+  </si>
+  <si>
+    <t>スヌーピーＸ型エプロン　スヌーピーカーキ</t>
+  </si>
+  <si>
+    <t>ミッフィーフード付き５ＷＡＹブランケット</t>
+  </si>
+  <si>
+    <t>サンリオ特大おみやげバッグ　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオ特大おみやげバッグ　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオ特大おみやげバッグ　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオ特大おみやげバッグ　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　ポチャッコ</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　ポムポムプリン</t>
+  </si>
+  <si>
+    <t>ＤＢラバーリールキーホルダー　ミッフィー</t>
+  </si>
+  <si>
+    <t>ＤＢラバーリールキーホルダー　ミッフィーフェイス</t>
+  </si>
+  <si>
+    <t>スヌーピーカラビナリールホルダー　チャーリー・ブラウン</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　スヌーピー</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　スヌーピー＆ウッドストック</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　ジョー・クール</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　レター</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　ウッドストック</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　チャーリーブラウン</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　ハンギョドン</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ポムポムプリン</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ポチャッコ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ハンギョドン</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ウサハナ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　マイスウィートピアノ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　こぎみゅん</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ぐでたま</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　タイニーチャム</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　グッドはな丸</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ミルク</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　マフィン</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ピィ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　さゆり</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　バク</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　バッドばつ丸</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　タキシードサム</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　けろけろけろっぴ</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃんカチューシャキーホルダー　しんのすけ</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　クロミ＆バクセット</t>
+  </si>
+  <si>
+    <t>サンリオぬいぐるみマスコット　シナモ＆ミルクセット</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　ドッグディッシュ２</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　ボックス</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　オラフ</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　フライングエース</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　アストロノーツ</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　キティ</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　ポチャッコ</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　ハンギョドン</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　みるく（シナモロール）</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　マフィン（ポムポムプリン）</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　ウィッシュミーメル</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　こぎみゅん</t>
+  </si>
+  <si>
+    <t>サンリオカチューシャキーホルダー　はなまるおばけ</t>
+  </si>
+  <si>
+    <t>サンリオバケットハットキーホルダー　はなまるおばけ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニニュースペーパーバッグＫＨ　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオふわふわしっぽキーホルダー　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオふわふわしっぽキーホルダー　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオふわふわしっぽキーホルダー　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオフルキャップキーホルダー　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオフルキャップキーホルダー　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオフルキャップキーホルダー　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオフルキャップキーホルダー　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオハートクッションマスコット　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオハートクッションマスコット　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオハートクッションマスコット　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオハートクッションマスコット　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　ポチャッコ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　ポムポムプリン</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　ハンギョドン</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　タキシードサム</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　けろけろけろっぴ</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　チョコキャット</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　マフィン</t>
+  </si>
+  <si>
+    <t>サンリオタータンチェックぬいぐるみマスコット　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオタータンチェックぬいぐるみマスコット　チョコキャット</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｍ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ａ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｋ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｒ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｙ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｓ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｈ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｎ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｔ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｃ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｅ</t>
+  </si>
+  <si>
+    <t>スヌーピーイニシャルキーホルダー　Ｉ</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃん３チャームキーホルダー　しんちゃんフェイス</t>
+  </si>
+  <si>
+    <t>クレヨンしんちゃん３チャームキーホルダー　しんちゃんとなかま</t>
+  </si>
+  <si>
+    <t>サンリオリボンメタルキーホルダー　はなまるおばけ</t>
+  </si>
+  <si>
+    <t>サンリオぬくいーず・ころほっぺつん　ハローキティ</t>
+  </si>
+  <si>
+    <t>サンリオぬくいーず・ころほっぺつん　マイメロディ</t>
+  </si>
+  <si>
+    <t>サンリオぬくいーず・ころほっぺつん　クロミ</t>
+  </si>
+  <si>
+    <t>サンリオぬくいーず・ころほっぺつん　シナモロール</t>
+  </si>
+  <si>
+    <t>サンリオミニミニフェイスコインケース　ウサハナ</t>
+  </si>
+  <si>
+    <t>スヌーピーミニアクリルチャーム　スヌーピーいっぱい</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック Light"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -62,15 +814,188 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -78,19 +1003,293 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="入力" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -421,42 +1620,4100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA79D641-7E02-4833-AF70-A28B1298A9DE}">
-  <dimension ref="B1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28435A72-83F4-4FED-AEDB-8F693A1B16AB}">
+  <dimension ref="A1:F204"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B2">
-        <v>4901234567890</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B3">
-        <v>4547274043587</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B4">
-        <v>4547274044041</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B5">
-        <v>4547274044065</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B6">
-        <v>4547274044072</v>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>311005</v>
+      </c>
+      <c r="B2" s="1">
+        <v>4518648365994</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1480</v>
+      </c>
+      <c r="F2">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>311007</v>
+      </c>
+      <c r="B3" s="1">
+        <v>4518648366014</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1480</v>
+      </c>
+      <c r="F3">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>311009</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4582723269262</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1680</v>
+      </c>
+      <c r="F4">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>311010</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4582723269279</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1680</v>
+      </c>
+      <c r="F5">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>311011</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4582723269286</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1680</v>
+      </c>
+      <c r="F6">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>311012</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4582723269293</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1680</v>
+      </c>
+      <c r="F7">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>311014</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4518648373524</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1680</v>
+      </c>
+      <c r="F8">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>311015</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4518648373531</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1680</v>
+      </c>
+      <c r="F9">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>311016</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4518648373548</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1680</v>
+      </c>
+      <c r="F10">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>311017</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4518648373555</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1680</v>
+      </c>
+      <c r="F11">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>402124</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4518648360760</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2300</v>
+      </c>
+      <c r="F12">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>402125</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4518648360777</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>2300</v>
+      </c>
+      <c r="F13">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>402127</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4518648371414</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>3000</v>
+      </c>
+      <c r="F14">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>402128</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4518648371421</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>3000</v>
+      </c>
+      <c r="F15">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>402133</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4518648371476</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>2300</v>
+      </c>
+      <c r="F16">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>402134</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4518648371483</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1600</v>
+      </c>
+      <c r="F17">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>402140</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4518648375696</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2300</v>
+      </c>
+      <c r="F18">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>402141</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4518648375702</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1600</v>
+      </c>
+      <c r="F19">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>402142</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4518648377669</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>2300</v>
+      </c>
+      <c r="F20">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>402143</v>
+      </c>
+      <c r="B21" s="1">
+        <v>4518648377676</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>2300</v>
+      </c>
+      <c r="F21">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>402144</v>
+      </c>
+      <c r="B22" s="1">
+        <v>4518648377683</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1600</v>
+      </c>
+      <c r="F22">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>402145</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4518648377690</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1600</v>
+      </c>
+      <c r="F23">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>404215</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4518648371513</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>900</v>
+      </c>
+      <c r="F24">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>404217</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4550376173816</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>780</v>
+      </c>
+      <c r="F25">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>404221</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4550376173854</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>780</v>
+      </c>
+      <c r="F26">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>404222</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4550376173861</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>780</v>
+      </c>
+      <c r="F27">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>404223</v>
+      </c>
+      <c r="B28" s="1">
+        <v>4550376173878</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>780</v>
+      </c>
+      <c r="F28">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>404224</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4550376173885</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>780</v>
+      </c>
+      <c r="F29">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>404228</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4550376208730</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>780</v>
+      </c>
+      <c r="F30">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>404229</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4550376208747</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>780</v>
+      </c>
+      <c r="F31">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>404230</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4550376208754</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>780</v>
+      </c>
+      <c r="F32">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>404231</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4550376208761</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>780</v>
+      </c>
+      <c r="F33">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>404232</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4550376208778</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>780</v>
+      </c>
+      <c r="F34">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>404233</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4550376208785</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>780</v>
+      </c>
+      <c r="F35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>404234</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4518648375337</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1500</v>
+      </c>
+      <c r="F36">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>404235</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4518648375719</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>900</v>
+      </c>
+      <c r="F37">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>405391</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4518648345224</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>390</v>
+      </c>
+      <c r="F38">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>405393</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4518648345248</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>390</v>
+      </c>
+      <c r="F39">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>405394</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4518648345255</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>390</v>
+      </c>
+      <c r="F40">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>405399</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4518648345385</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>390</v>
+      </c>
+      <c r="F41">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>405400</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4518648345392</v>
+      </c>
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>390</v>
+      </c>
+      <c r="F42">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>405401</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4518648345408</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>390</v>
+      </c>
+      <c r="F43">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>405402</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4518648345415</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>390</v>
+      </c>
+      <c r="F44">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>405403</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4518648345422</v>
+      </c>
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>390</v>
+      </c>
+      <c r="F45">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>405404</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4518648345439</v>
+      </c>
+      <c r="C46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>390</v>
+      </c>
+      <c r="F46">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>405405</v>
+      </c>
+      <c r="B47" s="1">
+        <v>4518648345446</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>390</v>
+      </c>
+      <c r="F47">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>405406</v>
+      </c>
+      <c r="B48" s="1">
+        <v>4518648345453</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>390</v>
+      </c>
+      <c r="F48">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>405407</v>
+      </c>
+      <c r="B49" s="1">
+        <v>4518648345460</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>390</v>
+      </c>
+      <c r="F49">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>405408</v>
+      </c>
+      <c r="B50" s="1">
+        <v>4518648345477</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>390</v>
+      </c>
+      <c r="F50">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>405416</v>
+      </c>
+      <c r="B51" s="1">
+        <v>4518648346474</v>
+      </c>
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>390</v>
+      </c>
+      <c r="F51">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>405417</v>
+      </c>
+      <c r="B52" s="1">
+        <v>4518648346481</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>390</v>
+      </c>
+      <c r="F52">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>405418</v>
+      </c>
+      <c r="B53" s="1">
+        <v>4518648346498</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>390</v>
+      </c>
+      <c r="F53">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>405419</v>
+      </c>
+      <c r="B54" s="1">
+        <v>4518648346504</v>
+      </c>
+      <c r="C54" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>390</v>
+      </c>
+      <c r="F54">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>405420</v>
+      </c>
+      <c r="B55" s="1">
+        <v>4518648346511</v>
+      </c>
+      <c r="C55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>390</v>
+      </c>
+      <c r="F55">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>405421</v>
+      </c>
+      <c r="B56" s="1">
+        <v>4518648346528</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>390</v>
+      </c>
+      <c r="F56">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>405423</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4518648346542</v>
+      </c>
+      <c r="C57" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>390</v>
+      </c>
+      <c r="F57">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>405426</v>
+      </c>
+      <c r="B58" s="1">
+        <v>4518648346573</v>
+      </c>
+      <c r="C58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>390</v>
+      </c>
+      <c r="F58">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>405427</v>
+      </c>
+      <c r="B59" s="1">
+        <v>4518648346580</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>390</v>
+      </c>
+      <c r="F59">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>405434</v>
+      </c>
+      <c r="B60" s="1">
+        <v>4518648346658</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>390</v>
+      </c>
+      <c r="F60">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>405439</v>
+      </c>
+      <c r="B61" s="1">
+        <v>4518648346702</v>
+      </c>
+      <c r="C61" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>390</v>
+      </c>
+      <c r="F61">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>405440</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4518648346719</v>
+      </c>
+      <c r="C62" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>390</v>
+      </c>
+      <c r="F62">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>405446</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4518648346771</v>
+      </c>
+      <c r="C63" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>390</v>
+      </c>
+      <c r="F63">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>405450</v>
+      </c>
+      <c r="B64" s="1">
+        <v>4518648347501</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>390</v>
+      </c>
+      <c r="F64">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>405451</v>
+      </c>
+      <c r="B65" s="1">
+        <v>4518648347518</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>390</v>
+      </c>
+      <c r="F65">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>405452</v>
+      </c>
+      <c r="B66" s="1">
+        <v>4518648347525</v>
+      </c>
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>390</v>
+      </c>
+      <c r="F66">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>405454</v>
+      </c>
+      <c r="B67" s="1">
+        <v>4518648347594</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>390</v>
+      </c>
+      <c r="F67">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>405455</v>
+      </c>
+      <c r="B68" s="1">
+        <v>4518648347600</v>
+      </c>
+      <c r="C68" t="s">
+        <v>71</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>390</v>
+      </c>
+      <c r="F68">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>405464</v>
+      </c>
+      <c r="B69" s="1">
+        <v>4518648353519</v>
+      </c>
+      <c r="C69" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>390</v>
+      </c>
+      <c r="F69">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>405482</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4518648357494</v>
+      </c>
+      <c r="C70" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>390</v>
+      </c>
+      <c r="F70">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>405485</v>
+      </c>
+      <c r="B71" s="1">
+        <v>4518648357524</v>
+      </c>
+      <c r="C71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>390</v>
+      </c>
+      <c r="F71">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>405491</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4518648361958</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>390</v>
+      </c>
+      <c r="F72">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>405492</v>
+      </c>
+      <c r="B73" s="1">
+        <v>4518648361972</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>390</v>
+      </c>
+      <c r="F73">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>405494</v>
+      </c>
+      <c r="B74" s="1">
+        <v>4518648362665</v>
+      </c>
+      <c r="C74" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>390</v>
+      </c>
+      <c r="F74">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>405497</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4518648362696</v>
+      </c>
+      <c r="C75" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>390</v>
+      </c>
+      <c r="F75">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>405498</v>
+      </c>
+      <c r="B76" s="1">
+        <v>4518648362702</v>
+      </c>
+      <c r="C76" t="s">
+        <v>79</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>390</v>
+      </c>
+      <c r="F76">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>405499</v>
+      </c>
+      <c r="B77" s="1">
+        <v>4518648362719</v>
+      </c>
+      <c r="C77" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>390</v>
+      </c>
+      <c r="F77">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>405501</v>
+      </c>
+      <c r="B78" s="1">
+        <v>4518648362825</v>
+      </c>
+      <c r="C78" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>390</v>
+      </c>
+      <c r="F78">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>405505</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4518648362863</v>
+      </c>
+      <c r="C79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>390</v>
+      </c>
+      <c r="F79">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>405508</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4518648365536</v>
+      </c>
+      <c r="C80" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>390</v>
+      </c>
+      <c r="F80">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>405511</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4573606190629</v>
+      </c>
+      <c r="C81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>500</v>
+      </c>
+      <c r="F81">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>405512</v>
+      </c>
+      <c r="B82" s="1">
+        <v>4573606190636</v>
+      </c>
+      <c r="C82" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>500</v>
+      </c>
+      <c r="F82">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>405513</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4573606190643</v>
+      </c>
+      <c r="C83" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>500</v>
+      </c>
+      <c r="F83">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>405514</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4573606190650</v>
+      </c>
+      <c r="C84" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>500</v>
+      </c>
+      <c r="F84">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>405515</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4573606190667</v>
+      </c>
+      <c r="C85" t="s">
+        <v>88</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>500</v>
+      </c>
+      <c r="F85">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>405516</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4573606190674</v>
+      </c>
+      <c r="C86" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>500</v>
+      </c>
+      <c r="F86">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>405518</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4518648374842</v>
+      </c>
+      <c r="C87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>390</v>
+      </c>
+      <c r="F87">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>405519</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4518648374859</v>
+      </c>
+      <c r="C88" t="s">
+        <v>91</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>390</v>
+      </c>
+      <c r="F88">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>406106</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4518648361842</v>
+      </c>
+      <c r="C89" t="s">
+        <v>92</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>3500</v>
+      </c>
+      <c r="F89">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>406109</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4518648363990</v>
+      </c>
+      <c r="C90" t="s">
+        <v>93</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>3500</v>
+      </c>
+      <c r="F90">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>406111</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4518648364027</v>
+      </c>
+      <c r="C91" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>3500</v>
+      </c>
+      <c r="F91">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>406112</v>
+      </c>
+      <c r="B92" s="1">
+        <v>4518648364034</v>
+      </c>
+      <c r="C92" t="s">
+        <v>95</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>3500</v>
+      </c>
+      <c r="F92">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>406120</v>
+      </c>
+      <c r="B93" s="1">
+        <v>4535519181095</v>
+      </c>
+      <c r="C93" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>3500</v>
+      </c>
+      <c r="F93">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>406121</v>
+      </c>
+      <c r="B94" s="1">
+        <v>4535519181101</v>
+      </c>
+      <c r="C94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>3500</v>
+      </c>
+      <c r="F94">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>406122</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4518648381857</v>
+      </c>
+      <c r="C95" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>3400</v>
+      </c>
+      <c r="F95">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>406123</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4518648381864</v>
+      </c>
+      <c r="C96" t="s">
+        <v>99</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>3400</v>
+      </c>
+      <c r="F96">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>411002</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4908092373872</v>
+      </c>
+      <c r="C97" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>3980</v>
+      </c>
+      <c r="F97">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>415001</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4991567716007</v>
+      </c>
+      <c r="C98" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1300</v>
+      </c>
+      <c r="F98">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>415002</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4991567716014</v>
+      </c>
+      <c r="C99" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>1300</v>
+      </c>
+      <c r="F99">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>415003</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4991567716021</v>
+      </c>
+      <c r="C100" t="s">
+        <v>103</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>1300</v>
+      </c>
+      <c r="F100">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>415004</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4991567716038</v>
+      </c>
+      <c r="C101" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1300</v>
+      </c>
+      <c r="F101">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>506444</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4518648340861</v>
+      </c>
+      <c r="C102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>880</v>
+      </c>
+      <c r="F102">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>506445</v>
+      </c>
+      <c r="B103" s="1">
+        <v>4518648340878</v>
+      </c>
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>880</v>
+      </c>
+      <c r="F103">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>506446</v>
+      </c>
+      <c r="B104" s="1">
+        <v>4518648340885</v>
+      </c>
+      <c r="C104" t="s">
+        <v>107</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>880</v>
+      </c>
+      <c r="F104">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>506447</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4518648340892</v>
+      </c>
+      <c r="C105" t="s">
+        <v>108</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>880</v>
+      </c>
+      <c r="F105">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>506448</v>
+      </c>
+      <c r="B106" s="1">
+        <v>4518648340908</v>
+      </c>
+      <c r="C106" t="s">
+        <v>109</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>880</v>
+      </c>
+      <c r="F106">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>506463</v>
+      </c>
+      <c r="B107" s="1">
+        <v>4571542967367</v>
+      </c>
+      <c r="C107" t="s">
+        <v>110</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>1000</v>
+      </c>
+      <c r="F107">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>506464</v>
+      </c>
+      <c r="B108" s="1">
+        <v>4571542967374</v>
+      </c>
+      <c r="C108" t="s">
+        <v>111</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>1000</v>
+      </c>
+      <c r="F108">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>506471</v>
+      </c>
+      <c r="B109" s="1">
+        <v>4518648344920</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>680</v>
+      </c>
+      <c r="F109">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>506477</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4518648346948</v>
+      </c>
+      <c r="C110" t="s">
+        <v>113</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>450</v>
+      </c>
+      <c r="F110">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>506478</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4518648346955</v>
+      </c>
+      <c r="C111" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>450</v>
+      </c>
+      <c r="F111">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>506479</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4518648346962</v>
+      </c>
+      <c r="C112" t="s">
+        <v>115</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112">
+        <v>450</v>
+      </c>
+      <c r="F112">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>506483</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4518648347006</v>
+      </c>
+      <c r="C113" t="s">
+        <v>116</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>450</v>
+      </c>
+      <c r="F113">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>506485</v>
+      </c>
+      <c r="B114" s="1">
+        <v>4518648347020</v>
+      </c>
+      <c r="C114" t="s">
+        <v>117</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>450</v>
+      </c>
+      <c r="F114">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>506486</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4518648347037</v>
+      </c>
+      <c r="C115" t="s">
+        <v>118</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>450</v>
+      </c>
+      <c r="F115">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>506497</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4518648350525</v>
+      </c>
+      <c r="C116" t="s">
+        <v>119</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>880</v>
+      </c>
+      <c r="F116">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>506508</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4518648353557</v>
+      </c>
+      <c r="C117" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>980</v>
+      </c>
+      <c r="F117">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>506509</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4518648353564</v>
+      </c>
+      <c r="C118" t="s">
+        <v>121</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>980</v>
+      </c>
+      <c r="F118">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>506510</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4518648353571</v>
+      </c>
+      <c r="C119" t="s">
+        <v>122</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="E119">
+        <v>980</v>
+      </c>
+      <c r="F119">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>506511</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4518648353588</v>
+      </c>
+      <c r="C120" t="s">
+        <v>123</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>980</v>
+      </c>
+      <c r="F120">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>506512</v>
+      </c>
+      <c r="B121" s="1">
+        <v>4518648353595</v>
+      </c>
+      <c r="C121" t="s">
+        <v>124</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>980</v>
+      </c>
+      <c r="F121">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>506513</v>
+      </c>
+      <c r="B122" s="1">
+        <v>4518648353601</v>
+      </c>
+      <c r="C122" t="s">
+        <v>125</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>980</v>
+      </c>
+      <c r="F122">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>506514</v>
+      </c>
+      <c r="B123" s="1">
+        <v>4518648353762</v>
+      </c>
+      <c r="C123" t="s">
+        <v>126</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>980</v>
+      </c>
+      <c r="F123">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>506515</v>
+      </c>
+      <c r="B124" s="1">
+        <v>4518648353779</v>
+      </c>
+      <c r="C124" t="s">
+        <v>127</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>980</v>
+      </c>
+      <c r="F124">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>506516</v>
+      </c>
+      <c r="B125" s="1">
+        <v>4518648353786</v>
+      </c>
+      <c r="C125" t="s">
+        <v>128</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>980</v>
+      </c>
+      <c r="F125">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>506517</v>
+      </c>
+      <c r="B126" s="1">
+        <v>4518648353793</v>
+      </c>
+      <c r="C126" t="s">
+        <v>129</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>980</v>
+      </c>
+      <c r="F126">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <v>506518</v>
+      </c>
+      <c r="B127" s="1">
+        <v>4518648353809</v>
+      </c>
+      <c r="C127" t="s">
+        <v>130</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>980</v>
+      </c>
+      <c r="F127">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <v>506519</v>
+      </c>
+      <c r="B128" s="1">
+        <v>4518648353816</v>
+      </c>
+      <c r="C128" t="s">
+        <v>131</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>980</v>
+      </c>
+      <c r="F128">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <v>506520</v>
+      </c>
+      <c r="B129" s="1">
+        <v>4518648353823</v>
+      </c>
+      <c r="C129" t="s">
+        <v>132</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>980</v>
+      </c>
+      <c r="F129">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>506521</v>
+      </c>
+      <c r="B130" s="1">
+        <v>4518648353830</v>
+      </c>
+      <c r="C130" t="s">
+        <v>133</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>980</v>
+      </c>
+      <c r="F130">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>506522</v>
+      </c>
+      <c r="B131" s="1">
+        <v>4518648353847</v>
+      </c>
+      <c r="C131" t="s">
+        <v>134</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>980</v>
+      </c>
+      <c r="F131">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>506523</v>
+      </c>
+      <c r="B132" s="1">
+        <v>4518648353854</v>
+      </c>
+      <c r="C132" t="s">
+        <v>135</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>980</v>
+      </c>
+      <c r="F132">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>506524</v>
+      </c>
+      <c r="B133" s="1">
+        <v>4518648353861</v>
+      </c>
+      <c r="C133" t="s">
+        <v>136</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>980</v>
+      </c>
+      <c r="F133">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>506525</v>
+      </c>
+      <c r="B134" s="1">
+        <v>4518648353878</v>
+      </c>
+      <c r="C134" t="s">
+        <v>137</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>980</v>
+      </c>
+      <c r="F134">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>506545</v>
+      </c>
+      <c r="B135" s="1">
+        <v>4518648356107</v>
+      </c>
+      <c r="C135" t="s">
+        <v>138</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>980</v>
+      </c>
+      <c r="F135">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>506546</v>
+      </c>
+      <c r="B136" s="1">
+        <v>4518648356114</v>
+      </c>
+      <c r="C136" t="s">
+        <v>139</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>980</v>
+      </c>
+      <c r="F136">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A137">
+        <v>506547</v>
+      </c>
+      <c r="B137" s="1">
+        <v>4518648356121</v>
+      </c>
+      <c r="C137" t="s">
+        <v>140</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>980</v>
+      </c>
+      <c r="F137">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A138">
+        <v>506548</v>
+      </c>
+      <c r="B138" s="1">
+        <v>4518648356138</v>
+      </c>
+      <c r="C138" t="s">
+        <v>141</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>980</v>
+      </c>
+      <c r="F138">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A139">
+        <v>506586</v>
+      </c>
+      <c r="B139" s="1">
+        <v>4582723268401</v>
+      </c>
+      <c r="C139" t="s">
+        <v>142</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>980</v>
+      </c>
+      <c r="F139">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A140">
+        <v>506601</v>
+      </c>
+      <c r="B140" s="1">
+        <v>4518648362498</v>
+      </c>
+      <c r="C140" t="s">
+        <v>143</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>1960</v>
+      </c>
+      <c r="F140">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A141">
+        <v>506602</v>
+      </c>
+      <c r="B141" s="1">
+        <v>4518648362504</v>
+      </c>
+      <c r="C141" t="s">
+        <v>144</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>1960</v>
+      </c>
+      <c r="F141">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A142">
+        <v>506609</v>
+      </c>
+      <c r="B142" s="1">
+        <v>4518648363907</v>
+      </c>
+      <c r="C142" t="s">
+        <v>145</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>450</v>
+      </c>
+      <c r="F142">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A143">
+        <v>506611</v>
+      </c>
+      <c r="B143" s="1">
+        <v>4518648363921</v>
+      </c>
+      <c r="C143" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>450</v>
+      </c>
+      <c r="F143">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A144">
+        <v>506612</v>
+      </c>
+      <c r="B144" s="1">
+        <v>4518648363938</v>
+      </c>
+      <c r="C144" t="s">
+        <v>147</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>450</v>
+      </c>
+      <c r="F144">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A145">
+        <v>506613</v>
+      </c>
+      <c r="B145" s="1">
+        <v>4518648363945</v>
+      </c>
+      <c r="C145" t="s">
+        <v>148</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145">
+        <v>450</v>
+      </c>
+      <c r="F145">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A146">
+        <v>506614</v>
+      </c>
+      <c r="B146" s="1">
+        <v>4518648363952</v>
+      </c>
+      <c r="C146" t="s">
+        <v>149</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>450</v>
+      </c>
+      <c r="F146">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A147">
+        <v>506616</v>
+      </c>
+      <c r="B147" s="1">
+        <v>4518648364102</v>
+      </c>
+      <c r="C147" t="s">
+        <v>150</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>900</v>
+      </c>
+      <c r="F147">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A148">
+        <v>506617</v>
+      </c>
+      <c r="B148" s="1">
+        <v>4518648364119</v>
+      </c>
+      <c r="C148" t="s">
+        <v>151</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148">
+        <v>900</v>
+      </c>
+      <c r="F148">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A149">
+        <v>506618</v>
+      </c>
+      <c r="B149" s="1">
+        <v>4518648364126</v>
+      </c>
+      <c r="C149" t="s">
+        <v>152</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149">
+        <v>900</v>
+      </c>
+      <c r="F149">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A150">
+        <v>506619</v>
+      </c>
+      <c r="B150" s="1">
+        <v>4518648364133</v>
+      </c>
+      <c r="C150" t="s">
+        <v>153</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>900</v>
+      </c>
+      <c r="F150">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A151">
+        <v>506620</v>
+      </c>
+      <c r="B151" s="1">
+        <v>4518648364140</v>
+      </c>
+      <c r="C151" t="s">
+        <v>154</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>900</v>
+      </c>
+      <c r="F151">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A152">
+        <v>506622</v>
+      </c>
+      <c r="B152" s="1">
+        <v>4518648364164</v>
+      </c>
+      <c r="C152" t="s">
+        <v>155</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>900</v>
+      </c>
+      <c r="F152">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A153">
+        <v>506623</v>
+      </c>
+      <c r="B153" s="1">
+        <v>4518648364171</v>
+      </c>
+      <c r="C153" t="s">
+        <v>156</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>900</v>
+      </c>
+      <c r="F153">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A154">
+        <v>506624</v>
+      </c>
+      <c r="B154" s="1">
+        <v>4518648364188</v>
+      </c>
+      <c r="C154" t="s">
+        <v>157</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154">
+        <v>900</v>
+      </c>
+      <c r="F154">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A155">
+        <v>506626</v>
+      </c>
+      <c r="B155" s="1">
+        <v>4518648364201</v>
+      </c>
+      <c r="C155" t="s">
+        <v>158</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>900</v>
+      </c>
+      <c r="F155">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A156">
+        <v>506627</v>
+      </c>
+      <c r="B156" s="1">
+        <v>4518648364218</v>
+      </c>
+      <c r="C156" t="s">
+        <v>159</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>900</v>
+      </c>
+      <c r="F156">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A157">
+        <v>506630</v>
+      </c>
+      <c r="B157" s="1">
+        <v>4518648365666</v>
+      </c>
+      <c r="C157" t="s">
+        <v>160</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>880</v>
+      </c>
+      <c r="F157">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A158">
+        <v>506631</v>
+      </c>
+      <c r="B158" s="1">
+        <v>4518648365673</v>
+      </c>
+      <c r="C158" t="s">
+        <v>161</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>980</v>
+      </c>
+      <c r="F158">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A159">
+        <v>506641</v>
+      </c>
+      <c r="B159" s="1">
+        <v>4518648368575</v>
+      </c>
+      <c r="C159" t="s">
+        <v>162</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>780</v>
+      </c>
+      <c r="F159">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A160">
+        <v>506647</v>
+      </c>
+      <c r="B160" s="1">
+        <v>4518648368902</v>
+      </c>
+      <c r="C160" t="s">
+        <v>163</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>1200</v>
+      </c>
+      <c r="F160">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A161">
+        <v>506649</v>
+      </c>
+      <c r="B161" s="1">
+        <v>4518648368926</v>
+      </c>
+      <c r="C161" t="s">
+        <v>164</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>1200</v>
+      </c>
+      <c r="F161">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A162">
+        <v>506650</v>
+      </c>
+      <c r="B162" s="1">
+        <v>4518648368933</v>
+      </c>
+      <c r="C162" t="s">
+        <v>165</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>1200</v>
+      </c>
+      <c r="F162">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A163">
+        <v>506652</v>
+      </c>
+      <c r="B163" s="1">
+        <v>4518648370905</v>
+      </c>
+      <c r="C163" t="s">
+        <v>166</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>1200</v>
+      </c>
+      <c r="F163">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A164">
+        <v>506653</v>
+      </c>
+      <c r="B164" s="1">
+        <v>4518648370912</v>
+      </c>
+      <c r="C164" t="s">
+        <v>167</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>1200</v>
+      </c>
+      <c r="F164">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A165">
+        <v>506654</v>
+      </c>
+      <c r="B165" s="1">
+        <v>4518648370929</v>
+      </c>
+      <c r="C165" t="s">
+        <v>168</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>1200</v>
+      </c>
+      <c r="F165">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A166">
+        <v>506655</v>
+      </c>
+      <c r="B166" s="1">
+        <v>4518648370936</v>
+      </c>
+      <c r="C166" t="s">
+        <v>169</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>1200</v>
+      </c>
+      <c r="F166">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A167">
+        <v>506657</v>
+      </c>
+      <c r="B167" s="1">
+        <v>4518648371001</v>
+      </c>
+      <c r="C167" t="s">
+        <v>170</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>1200</v>
+      </c>
+      <c r="F167">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A168">
+        <v>506658</v>
+      </c>
+      <c r="B168" s="1">
+        <v>4518648371018</v>
+      </c>
+      <c r="C168" t="s">
+        <v>171</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>1200</v>
+      </c>
+      <c r="F168">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A169">
+        <v>506659</v>
+      </c>
+      <c r="B169" s="1">
+        <v>4518648371025</v>
+      </c>
+      <c r="C169" t="s">
+        <v>172</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>1200</v>
+      </c>
+      <c r="F169">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A170">
+        <v>506660</v>
+      </c>
+      <c r="B170" s="1">
+        <v>4518648371032</v>
+      </c>
+      <c r="C170" t="s">
+        <v>173</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>1200</v>
+      </c>
+      <c r="F170">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A171">
+        <v>506662</v>
+      </c>
+      <c r="B171" s="1">
+        <v>4518648371087</v>
+      </c>
+      <c r="C171" t="s">
+        <v>174</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>780</v>
+      </c>
+      <c r="F171">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A172">
+        <v>506663</v>
+      </c>
+      <c r="B172" s="1">
+        <v>4518648371094</v>
+      </c>
+      <c r="C172" t="s">
+        <v>175</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172">
+        <v>780</v>
+      </c>
+      <c r="F172">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A173">
+        <v>506664</v>
+      </c>
+      <c r="B173" s="1">
+        <v>4518648371100</v>
+      </c>
+      <c r="C173" t="s">
+        <v>176</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>780</v>
+      </c>
+      <c r="F173">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A174">
+        <v>506665</v>
+      </c>
+      <c r="B174" s="1">
+        <v>4518648371117</v>
+      </c>
+      <c r="C174" t="s">
+        <v>177</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>780</v>
+      </c>
+      <c r="F174">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A175">
+        <v>506666</v>
+      </c>
+      <c r="B175" s="1">
+        <v>4518648371124</v>
+      </c>
+      <c r="C175" t="s">
+        <v>178</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>780</v>
+      </c>
+      <c r="F175">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A176">
+        <v>506667</v>
+      </c>
+      <c r="B176" s="1">
+        <v>4518648371131</v>
+      </c>
+      <c r="C176" t="s">
+        <v>179</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>780</v>
+      </c>
+      <c r="F176">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A177">
+        <v>506668</v>
+      </c>
+      <c r="B177" s="1">
+        <v>4518648371148</v>
+      </c>
+      <c r="C177" t="s">
+        <v>180</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>780</v>
+      </c>
+      <c r="F177">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A178">
+        <v>506669</v>
+      </c>
+      <c r="B178" s="1">
+        <v>4518648371155</v>
+      </c>
+      <c r="C178" t="s">
+        <v>181</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>780</v>
+      </c>
+      <c r="F178">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A179">
+        <v>506671</v>
+      </c>
+      <c r="B179" s="1">
+        <v>4518648371179</v>
+      </c>
+      <c r="C179" t="s">
+        <v>182</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>780</v>
+      </c>
+      <c r="F179">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A180">
+        <v>506672</v>
+      </c>
+      <c r="B180" s="1">
+        <v>4518648371186</v>
+      </c>
+      <c r="C180" t="s">
+        <v>183</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+      <c r="E180">
+        <v>780</v>
+      </c>
+      <c r="F180">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A181">
+        <v>506673</v>
+      </c>
+      <c r="B181" s="1">
+        <v>4518648371193</v>
+      </c>
+      <c r="C181" t="s">
+        <v>184</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>780</v>
+      </c>
+      <c r="F181">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A182">
+        <v>506675</v>
+      </c>
+      <c r="B182" s="1">
+        <v>4518648371384</v>
+      </c>
+      <c r="C182" t="s">
+        <v>185</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="E182">
+        <v>1100</v>
+      </c>
+      <c r="F182">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A183">
+        <v>506676</v>
+      </c>
+      <c r="B183" s="1">
+        <v>4518648371391</v>
+      </c>
+      <c r="C183" t="s">
+        <v>186</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>1100</v>
+      </c>
+      <c r="F183">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A184">
+        <v>506678</v>
+      </c>
+      <c r="B184" s="1">
+        <v>4518648371759</v>
+      </c>
+      <c r="C184" t="s">
+        <v>187</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>600</v>
+      </c>
+      <c r="F184">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A185">
+        <v>506679</v>
+      </c>
+      <c r="B185" s="1">
+        <v>4518648371766</v>
+      </c>
+      <c r="C185" t="s">
+        <v>188</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>600</v>
+      </c>
+      <c r="F185">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A186">
+        <v>506680</v>
+      </c>
+      <c r="B186" s="1">
+        <v>4518648371773</v>
+      </c>
+      <c r="C186" t="s">
+        <v>189</v>
+      </c>
+      <c r="D186">
+        <v>1</v>
+      </c>
+      <c r="E186">
+        <v>600</v>
+      </c>
+      <c r="F186">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A187">
+        <v>506681</v>
+      </c>
+      <c r="B187" s="1">
+        <v>4518648371780</v>
+      </c>
+      <c r="C187" t="s">
+        <v>190</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>600</v>
+      </c>
+      <c r="F187">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A188">
+        <v>506682</v>
+      </c>
+      <c r="B188" s="1">
+        <v>4518648371797</v>
+      </c>
+      <c r="C188" t="s">
+        <v>191</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>600</v>
+      </c>
+      <c r="F188">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A189">
+        <v>506683</v>
+      </c>
+      <c r="B189" s="1">
+        <v>4518648371803</v>
+      </c>
+      <c r="C189" t="s">
+        <v>192</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>600</v>
+      </c>
+      <c r="F189">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A190">
+        <v>506684</v>
+      </c>
+      <c r="B190" s="1">
+        <v>4518648371810</v>
+      </c>
+      <c r="C190" t="s">
+        <v>193</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>600</v>
+      </c>
+      <c r="F190">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A191">
+        <v>506685</v>
+      </c>
+      <c r="B191" s="1">
+        <v>4518648371827</v>
+      </c>
+      <c r="C191" t="s">
+        <v>194</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>600</v>
+      </c>
+      <c r="F191">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A192">
+        <v>506686</v>
+      </c>
+      <c r="B192" s="1">
+        <v>4518648371834</v>
+      </c>
+      <c r="C192" t="s">
+        <v>195</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>600</v>
+      </c>
+      <c r="F192">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A193">
+        <v>506687</v>
+      </c>
+      <c r="B193" s="1">
+        <v>4518648371841</v>
+      </c>
+      <c r="C193" t="s">
+        <v>196</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193">
+        <v>600</v>
+      </c>
+      <c r="F193">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A194">
+        <v>506688</v>
+      </c>
+      <c r="B194" s="1">
+        <v>4518648371858</v>
+      </c>
+      <c r="C194" t="s">
+        <v>197</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>600</v>
+      </c>
+      <c r="F194">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A195">
+        <v>506689</v>
+      </c>
+      <c r="B195" s="1">
+        <v>4518648371865</v>
+      </c>
+      <c r="C195" t="s">
+        <v>198</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
+      </c>
+      <c r="E195">
+        <v>600</v>
+      </c>
+      <c r="F195">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A196">
+        <v>506703</v>
+      </c>
+      <c r="B196" s="1">
+        <v>4548626257881</v>
+      </c>
+      <c r="C196" t="s">
+        <v>199</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196">
+        <v>880</v>
+      </c>
+      <c r="F196">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A197">
+        <v>506704</v>
+      </c>
+      <c r="B197" s="1">
+        <v>4548626257898</v>
+      </c>
+      <c r="C197" t="s">
+        <v>200</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>880</v>
+      </c>
+      <c r="F197">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A198">
+        <v>506717</v>
+      </c>
+      <c r="B198" s="1">
+        <v>4518648374712</v>
+      </c>
+      <c r="C198" t="s">
+        <v>201</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198">
+        <v>900</v>
+      </c>
+      <c r="F198">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A199">
+        <v>506718</v>
+      </c>
+      <c r="B199" s="1">
+        <v>4518648374729</v>
+      </c>
+      <c r="C199" t="s">
+        <v>202</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="E199">
+        <v>1380</v>
+      </c>
+      <c r="F199">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A200">
+        <v>506719</v>
+      </c>
+      <c r="B200" s="1">
+        <v>4518648374736</v>
+      </c>
+      <c r="C200" t="s">
+        <v>203</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200">
+        <v>1380</v>
+      </c>
+      <c r="F200">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A201">
+        <v>506720</v>
+      </c>
+      <c r="B201" s="1">
+        <v>4518648374743</v>
+      </c>
+      <c r="C201" t="s">
+        <v>204</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201">
+        <v>1380</v>
+      </c>
+      <c r="F201">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A202">
+        <v>506721</v>
+      </c>
+      <c r="B202" s="1">
+        <v>4518648374750</v>
+      </c>
+      <c r="C202" t="s">
+        <v>205</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>1380</v>
+      </c>
+      <c r="F202">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A203">
+        <v>506725</v>
+      </c>
+      <c r="B203" s="1">
+        <v>4518648375726</v>
+      </c>
+      <c r="C203" t="s">
+        <v>206</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>780</v>
+      </c>
+      <c r="F203">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A204">
+        <v>506727</v>
+      </c>
+      <c r="B204" s="1">
+        <v>4518648376150</v>
+      </c>
+      <c r="C204" t="s">
+        <v>207</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204">
+        <v>450</v>
+      </c>
+      <c r="F204">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>